--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="37">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,7 +19,7 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Caliente vs Tecos</t>
+    <t>Juego Inaugural: Charros vs Tecos</t>
   </si>
   <si>
     <t>ZONA</t>
@@ -85,58 +85,43 @@
     <t>-</t>
   </si>
   <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>Butaca General</t>
+  </si>
+  <si>
+    <t>4.09%</t>
+  </si>
+  <si>
+    <t>Butaca Preferente</t>
+  </si>
+  <si>
+    <t>26.32%</t>
+  </si>
+  <si>
+    <t>Gradas</t>
+  </si>
+  <si>
+    <t>Palcos</t>
+  </si>
+  <si>
     <t>100.00%</t>
   </si>
   <si>
-    <t>Butaca General</t>
-  </si>
-  <si>
-    <t>99.80%</t>
-  </si>
-  <si>
-    <t>Butaca Preferente</t>
-  </si>
-  <si>
-    <t>99.67%</t>
-  </si>
-  <si>
-    <t>Especial</t>
-  </si>
-  <si>
-    <t>26.00%</t>
-  </si>
-  <si>
-    <t>Gradas</t>
-  </si>
-  <si>
-    <t>39.75%</t>
-  </si>
-  <si>
-    <t>Palcos</t>
-  </si>
-  <si>
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>98.15%</t>
-  </si>
-  <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>SUITE</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
     <t>Tecobar</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.39%</t>
+    <t>4.57%</t>
   </si>
 </sst>
 </file>
@@ -567,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -660,8 +645,8 @@
       <c r="B6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="7">
-        <v>100</v>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>23</v>
@@ -702,11 +687,11 @@
       <c r="P6" s="7">
         <v>100</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" s="7">
         <v>100</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="S6" s="8" t="s">
         <v>24</v>
@@ -719,14 +704,14 @@
       <c r="B7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="7">
-        <v>466</v>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="7">
-        <v>55</v>
+      <c r="E7" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>23</v>
@@ -737,8 +722,8 @@
       <c r="H7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="7">
-        <v>474</v>
+      <c r="I7" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>23</v>
@@ -756,16 +741,16 @@
         <v>23</v>
       </c>
       <c r="O7" s="7">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="P7" s="7">
         <v>1003</v>
       </c>
       <c r="Q7" s="7">
-        <v>1001</v>
+        <v>41</v>
       </c>
       <c r="R7" s="7">
-        <v>2</v>
+        <v>962</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>26</v>
@@ -778,8 +763,8 @@
       <c r="B8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="7">
-        <v>217</v>
+      <c r="C8" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>23</v>
@@ -797,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="I8" s="7">
-        <v>385</v>
+        <v>159</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>23</v>
@@ -821,10 +806,10 @@
         <v>604</v>
       </c>
       <c r="Q8" s="7">
-        <v>602</v>
+        <v>159</v>
       </c>
       <c r="R8" s="7">
-        <v>2</v>
+        <v>445</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>28</v>
@@ -843,8 +828,8 @@
       <c r="D9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="7">
-        <v>26</v>
+      <c r="E9" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>23</v>
@@ -877,80 +862,80 @@
         <v>23</v>
       </c>
       <c r="P9" s="7">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="7">
-        <v>26</v>
+        <v>2800</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="R9" s="7">
-        <v>74</v>
+        <v>2800</v>
       </c>
       <c r="S9" s="8" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="7">
+        <v>24</v>
+      </c>
+      <c r="P10" s="7">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>24</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7">
-        <v>828</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="7">
-        <v>285</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P10" s="7">
-        <v>2800</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>1113</v>
-      </c>
-      <c r="R10" s="7">
-        <v>1687</v>
-      </c>
-      <c r="S10" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>23</v>
@@ -961,8 +946,8 @@
       <c r="D11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="7">
-        <v>16</v>
+      <c r="E11" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>23</v>
@@ -991,17 +976,17 @@
       <c r="N11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="O11" s="7">
-        <v>8</v>
+      <c r="O11" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="P11" s="7">
-        <v>24</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>24</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>23</v>
+        <v>108</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R11" s="7">
+        <v>108</v>
       </c>
       <c r="S11" s="8" t="s">
         <v>24</v>
@@ -1009,13 +994,13 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="7">
-        <v>34</v>
+      <c r="C12" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>23</v>
@@ -1032,8 +1017,8 @@
       <c r="H12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="7">
-        <v>72</v>
+      <c r="I12" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>23</v>
@@ -1056,25 +1041,25 @@
       <c r="P12" s="7">
         <v>108</v>
       </c>
-      <c r="Q12" s="7">
-        <v>106</v>
+      <c r="Q12" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="R12" s="7">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="S12" s="8" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="7">
-        <v>36</v>
+      <c r="C13" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>23</v>
@@ -1091,8 +1076,8 @@
       <c r="H13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="7">
-        <v>72</v>
+      <c r="I13" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>23</v>
@@ -1113,197 +1098,79 @@
         <v>23</v>
       </c>
       <c r="P13" s="7">
-        <v>108</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>108</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>23</v>
+        <v>150</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R13" s="7">
+        <v>150</v>
       </c>
       <c r="S13" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P14" s="7">
-        <v>20</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R14" s="7">
-        <v>20</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="9">
+        <f>SUM(B6:B13)</f>
+      </c>
+      <c r="C14" s="9">
+        <f>SUM(C6:C13)</f>
+      </c>
+      <c r="D14" s="9">
+        <f>SUM(D6:D13)</f>
+      </c>
+      <c r="E14" s="9">
+        <f>SUM(E6:E13)</f>
+      </c>
+      <c r="F14" s="9">
+        <f>SUM(F6:F13)</f>
+      </c>
+      <c r="G14" s="9">
+        <f>SUM(G6:G13)</f>
+      </c>
+      <c r="H14" s="9">
+        <f>SUM(H6:H13)</f>
+      </c>
+      <c r="I14" s="9">
+        <f>SUM(I6:I13)</f>
+      </c>
+      <c r="J14" s="9">
+        <f>SUM(J6:J13)</f>
+      </c>
+      <c r="K14" s="9">
+        <f>SUM(K6:K13)</f>
+      </c>
+      <c r="L14" s="9">
+        <f>SUM(L6:L13)</f>
+      </c>
+      <c r="M14" s="9">
+        <f>SUM(M6:M13)</f>
+      </c>
+      <c r="N14" s="9">
+        <f>SUM(N6:N13)</f>
+      </c>
+      <c r="O14" s="9">
+        <f>SUM(O6:O13)</f>
+      </c>
+      <c r="P14" s="9">
+        <f>SUM(P6:P13)</f>
+      </c>
+      <c r="Q14" s="9">
+        <f>SUM(Q6:Q13)</f>
+      </c>
+      <c r="R14" s="9">
+        <f>SUM(R6:R13)</f>
+      </c>
+      <c r="S14" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P15" s="7">
-        <v>150</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R15" s="7">
-        <v>150</v>
-      </c>
-      <c r="S15" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="9">
-        <f>SUM(B6:B15)</f>
-      </c>
-      <c r="C16" s="9">
-        <f>SUM(C6:C15)</f>
-      </c>
-      <c r="D16" s="9">
-        <f>SUM(D6:D15)</f>
-      </c>
-      <c r="E16" s="9">
-        <f>SUM(E6:E15)</f>
-      </c>
-      <c r="F16" s="9">
-        <f>SUM(F6:F15)</f>
-      </c>
-      <c r="G16" s="9">
-        <f>SUM(G6:G15)</f>
-      </c>
-      <c r="H16" s="9">
-        <f>SUM(H6:H15)</f>
-      </c>
-      <c r="I16" s="9">
-        <f>SUM(I6:I15)</f>
-      </c>
-      <c r="J16" s="9">
-        <f>SUM(J6:J15)</f>
-      </c>
-      <c r="K16" s="9">
-        <f>SUM(K6:K15)</f>
-      </c>
-      <c r="L16" s="9">
-        <f>SUM(L6:L15)</f>
-      </c>
-      <c r="M16" s="9">
-        <f>SUM(M6:M15)</f>
-      </c>
-      <c r="N16" s="9">
-        <f>SUM(N6:N15)</f>
-      </c>
-      <c r="O16" s="9">
-        <f>SUM(O6:O15)</f>
-      </c>
-      <c r="P16" s="9">
-        <f>SUM(P6:P15)</f>
-      </c>
-      <c r="Q16" s="9">
-        <f>SUM(Q6:Q15)</f>
-      </c>
-      <c r="R16" s="9">
-        <f>SUM(R6:R15)</f>
-      </c>
-      <c r="S16" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -97,7 +97,7 @@
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>26.32%</t>
+    <t>30.46%</t>
   </si>
   <si>
     <t>Gradas</t>
@@ -121,7 +121,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>4.57%</t>
+    <t>5.08%</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,7 @@
         <v>23</v>
       </c>
       <c r="I8" s="7">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>23</v>
@@ -806,10 +806,10 @@
         <v>604</v>
       </c>
       <c r="Q8" s="7">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="R8" s="7">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>28</v>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="38">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -25,10 +25,10 @@
     <t>ZONA</t>
   </si>
   <si>
-    <t>EN PROCESO DE VENTA</t>
-  </si>
-  <si>
-    <t>VENDIDOS CON PRECIO</t>
+    <t>AFORO</t>
+  </si>
+  <si>
+    <t>VENDIDOS</t>
   </si>
   <si>
     <t>PROMOS</t>
@@ -61,16 +61,13 @@
     <t>PAQUETES PRECIO $1</t>
   </si>
   <si>
-    <t>PROMOCIONES</t>
-  </si>
-  <si>
     <t>BLOQUEOS</t>
   </si>
   <si>
-    <t>AFORO</t>
-  </si>
-  <si>
-    <t>OCUPADOS</t>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>DISPONIBLES</t>
@@ -91,13 +88,13 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>4.09%</t>
+    <t>30.04%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>30.46%</t>
+    <t>50.34%</t>
   </si>
   <si>
     <t>Gradas</t>
@@ -112,16 +109,22 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
+    <t>33.33%</t>
+  </si>
+  <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
+    <t>44.44%</t>
+  </si>
+  <si>
     <t>Tecobar</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>5.08%</t>
+    <t>16.38%</t>
   </si>
 </sst>
 </file>
@@ -181,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -198,20 +201,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,11 +546,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="19" width="25" customWidth="1"/>
+    <col min="2" max="18" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -579,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -634,539 +628,509 @@
       <c r="R5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="S5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6">
+        <v>100</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>100</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="6">
+        <v>566</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="6">
+        <v>170</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" s="6">
+        <v>170</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>396</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1041</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="6">
+        <v>524</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="6">
+        <v>524</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>517</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2800</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>2800</v>
+      </c>
+      <c r="R9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" s="7">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" s="7">
-        <v>100</v>
-      </c>
-      <c r="S6" s="8" t="s">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="6">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="7">
-        <v>41</v>
-      </c>
-      <c r="P7" s="7">
-        <v>1003</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>41</v>
-      </c>
-      <c r="R7" s="7">
-        <v>962</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="7">
-        <v>184</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="7">
-        <v>604</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>184</v>
-      </c>
-      <c r="R8" s="7">
-        <v>420</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="7">
-        <v>2800</v>
-      </c>
-      <c r="Q9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R9" s="7">
-        <v>2800</v>
-      </c>
-      <c r="S9" s="8" t="s">
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="6">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="O10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="6">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="7">
-        <v>24</v>
-      </c>
-      <c r="P10" s="7">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>24</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="6">
+        <v>108</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="6">
+        <v>36</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="6">
+        <v>36</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>72</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P11" s="7">
-        <v>108</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R11" s="7">
-        <v>108</v>
-      </c>
-      <c r="S11" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6">
+        <v>108</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="6">
+        <v>48</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="6">
+        <v>48</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>60</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="6">
+        <v>150</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>150</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P12" s="7">
-        <v>108</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R12" s="7">
-        <v>108</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P13" s="7">
-        <v>150</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="R13" s="7">
-        <v>150</v>
-      </c>
-      <c r="S13" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="9">
+        <v>36</v>
+      </c>
+      <c r="B14" s="7">
         <f>SUM(B6:B13)</f>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <f>SUM(C6:C13)</f>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <f>SUM(D6:D13)</f>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="7">
         <f>SUM(E6:E13)</f>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="7">
         <f>SUM(F6:F13)</f>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="7">
         <f>SUM(G6:G13)</f>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <f>SUM(H6:H13)</f>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="7">
         <f>SUM(I6:I13)</f>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="7">
         <f>SUM(J6:J13)</f>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="7">
         <f>SUM(K6:K13)</f>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="7">
         <f>SUM(L6:L13)</f>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="7">
         <f>SUM(M6:M13)</f>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="7">
         <f>SUM(N6:N13)</f>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="7">
         <f>SUM(O6:O13)</f>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="7">
         <f>SUM(P6:P13)</f>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q14" s="7">
         <f>SUM(Q6:Q13)</f>
       </c>
-      <c r="R14" s="9">
-        <f>SUM(R6:R13)</f>
-      </c>
-      <c r="S14" s="10" t="s">
-        <v>36</v>
+      <c r="R14" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="39">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,13 +88,16 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>30.04%</t>
+    <t>31.10%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>50.34%</t>
+    <t>50.91%</t>
+  </si>
+  <si>
+    <t>Especial</t>
   </si>
   <si>
     <t>Gradas</t>
@@ -124,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>16.38%</t>
+    <t>16.29%</t>
   </si>
 </sst>
 </file>
@@ -546,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -711,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -732,10 +735,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="Q7" s="6">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -767,7 +770,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -788,10 +791,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="Q8" s="6">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -802,7 +805,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="6">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>22</v>
@@ -847,7 +850,7 @@
         <v>22</v>
       </c>
       <c r="Q9" s="6">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>23</v>
@@ -858,7 +861,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="6">
-        <v>24</v>
+        <v>2800</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>22</v>
@@ -893,81 +896,81 @@
       <c r="M10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="6">
-        <v>24</v>
+      <c r="N10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="6">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>22</v>
+      <c r="P10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>2800</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>24</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="6">
+        <v>24</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="6">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B11" s="6">
-        <v>108</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="6">
-        <v>36</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="6">
-        <v>36</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>72</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>108</v>
@@ -991,7 +994,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1012,129 +1015,185 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q12" s="6">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="6">
+        <v>108</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="6">
+        <v>48</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" s="6">
+        <v>48</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>60</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="6">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="6">
         <v>150</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q13" s="6">
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="6">
         <v>150</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="R14" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="7">
-        <f>SUM(B6:B13)</f>
-      </c>
-      <c r="C14" s="7">
-        <f>SUM(C6:C13)</f>
-      </c>
-      <c r="D14" s="7">
-        <f>SUM(D6:D13)</f>
-      </c>
-      <c r="E14" s="7">
-        <f>SUM(E6:E13)</f>
-      </c>
-      <c r="F14" s="7">
-        <f>SUM(F6:F13)</f>
-      </c>
-      <c r="G14" s="7">
-        <f>SUM(G6:G13)</f>
-      </c>
-      <c r="H14" s="7">
-        <f>SUM(H6:H13)</f>
-      </c>
-      <c r="I14" s="7">
-        <f>SUM(I6:I13)</f>
-      </c>
-      <c r="J14" s="7">
-        <f>SUM(J6:J13)</f>
-      </c>
-      <c r="K14" s="7">
-        <f>SUM(K6:K13)</f>
-      </c>
-      <c r="L14" s="7">
-        <f>SUM(L6:L13)</f>
-      </c>
-      <c r="M14" s="7">
-        <f>SUM(M6:M13)</f>
-      </c>
-      <c r="N14" s="7">
-        <f>SUM(N6:N13)</f>
-      </c>
-      <c r="O14" s="7">
-        <f>SUM(O6:O13)</f>
-      </c>
-      <c r="P14" s="7">
-        <f>SUM(P6:P13)</f>
-      </c>
-      <c r="Q14" s="7">
-        <f>SUM(Q6:Q13)</f>
-      </c>
-      <c r="R14" s="7" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="7">
+        <f>SUM(B6:B14)</f>
+      </c>
+      <c r="C15" s="7">
+        <f>SUM(C6:C14)</f>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D6:D14)</f>
+      </c>
+      <c r="E15" s="7">
+        <f>SUM(E6:E14)</f>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(F6:F14)</f>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(G6:G14)</f>
+      </c>
+      <c r="H15" s="7">
+        <f>SUM(H6:H14)</f>
+      </c>
+      <c r="I15" s="7">
+        <f>SUM(I6:I14)</f>
+      </c>
+      <c r="J15" s="7">
+        <f>SUM(J6:J14)</f>
+      </c>
+      <c r="K15" s="7">
+        <f>SUM(K6:K14)</f>
+      </c>
+      <c r="L15" s="7">
+        <f>SUM(L6:L14)</f>
+      </c>
+      <c r="M15" s="7">
+        <f>SUM(M6:M14)</f>
+      </c>
+      <c r="N15" s="7">
+        <f>SUM(N6:N14)</f>
+      </c>
+      <c r="O15" s="7">
+        <f>SUM(O6:O14)</f>
+      </c>
+      <c r="P15" s="7">
+        <f>SUM(P6:P14)</f>
+      </c>
+      <c r="Q15" s="7">
+        <f>SUM(Q6:Q14)</f>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,7 +19,7 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Charros vs Tecos</t>
+    <t>Juego Inaugural: Caliente vs Tecos</t>
   </si>
   <si>
     <t>ZONA</t>
@@ -82,52 +82,58 @@
     <t>-</t>
   </si>
   <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>Butaca General</t>
+  </si>
+  <si>
+    <t>99.80%</t>
+  </si>
+  <si>
+    <t>Butaca Preferente</t>
+  </si>
+  <si>
+    <t>99.67%</t>
+  </si>
+  <si>
+    <t>Especial</t>
+  </si>
+  <si>
+    <t>26.00%</t>
+  </si>
+  <si>
+    <t>Gradas</t>
+  </si>
+  <si>
+    <t>39.75%</t>
+  </si>
+  <si>
+    <t>Palcos</t>
+  </si>
+  <si>
+    <t>Palcos 1ra</t>
+  </si>
+  <si>
+    <t>98.15%</t>
+  </si>
+  <si>
+    <t>Palcos 3ra</t>
+  </si>
+  <si>
+    <t>SUITE</t>
+  </si>
+  <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>Butaca General</t>
-  </si>
-  <si>
-    <t>31.10%</t>
-  </si>
-  <si>
-    <t>Butaca Preferente</t>
-  </si>
-  <si>
-    <t>50.91%</t>
-  </si>
-  <si>
-    <t>Especial</t>
-  </si>
-  <si>
-    <t>Gradas</t>
-  </si>
-  <si>
-    <t>Palcos</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>Palcos 1ra</t>
-  </si>
-  <si>
-    <t>33.33%</t>
-  </si>
-  <si>
-    <t>Palcos 3ra</t>
-  </si>
-  <si>
-    <t>44.44%</t>
-  </si>
-  <si>
     <t>Tecobar</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>16.29%</t>
+    <t>61.39%</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -639,8 +645,8 @@
       <c r="B6" s="6">
         <v>100</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
+      <c r="C6" s="6">
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -678,11 +684,11 @@
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" s="6">
+      <c r="P6" s="6">
         <v>100</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -693,16 +699,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>566</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
+        <v>1003</v>
+      </c>
+      <c r="C7" s="6">
+        <v>466</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>55</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -714,7 +720,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>176</v>
+        <v>474</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -728,17 +734,17 @@
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>22</v>
+      <c r="N7" s="6">
+        <v>6</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>176</v>
+        <v>1001</v>
       </c>
       <c r="Q7" s="6">
-        <v>390</v>
+        <v>2</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -749,10 +755,10 @@
         <v>26</v>
       </c>
       <c r="B8" s="6">
-        <v>1041</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
+        <v>604</v>
+      </c>
+      <c r="C8" s="6">
+        <v>217</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -770,7 +776,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -791,10 +797,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>530</v>
+        <v>602</v>
       </c>
       <c r="Q8" s="6">
-        <v>511</v>
+        <v>2</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -813,8 +819,8 @@
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+      <c r="E9" s="6">
+        <v>26</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -846,31 +852,31 @@
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>22</v>
+      <c r="P9" s="6">
+        <v>26</v>
       </c>
       <c r="Q9" s="6">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6">
         <v>2800</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
+      <c r="C10" s="6">
+        <v>828</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
+      <c r="E10" s="6">
+        <v>285</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -902,19 +908,19 @@
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="6" t="s">
-        <v>22</v>
+      <c r="P10" s="6">
+        <v>1113</v>
       </c>
       <c r="Q10" s="6">
-        <v>2800</v>
+        <v>1687</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B11" s="6">
         <v>24</v>
@@ -925,8 +931,8 @@
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+      <c r="E11" s="6">
+        <v>16</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -953,7 +959,7 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -965,18 +971,18 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>108</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
+      <c r="C12" s="6">
+        <v>34</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -994,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1015,24 +1021,24 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="Q12" s="6">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6">
         <v>108</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
+      <c r="C13" s="6">
+        <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1050,7 +1056,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="6">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1071,13 +1077,13 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>48</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>60</v>
+        <v>108</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1085,115 +1091,171 @@
         <v>36</v>
       </c>
       <c r="B14" s="6">
+        <v>20</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>20</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="6">
         <v>150</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q14" s="6">
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="6">
         <v>150</v>
       </c>
-      <c r="R14" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="R15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(B6:B14)</f>
-      </c>
-      <c r="C15" s="7">
-        <f>SUM(C6:C14)</f>
-      </c>
-      <c r="D15" s="7">
-        <f>SUM(D6:D14)</f>
-      </c>
-      <c r="E15" s="7">
-        <f>SUM(E6:E14)</f>
-      </c>
-      <c r="F15" s="7">
-        <f>SUM(F6:F14)</f>
-      </c>
-      <c r="G15" s="7">
-        <f>SUM(G6:G14)</f>
-      </c>
-      <c r="H15" s="7">
-        <f>SUM(H6:H14)</f>
-      </c>
-      <c r="I15" s="7">
-        <f>SUM(I6:I14)</f>
-      </c>
-      <c r="J15" s="7">
-        <f>SUM(J6:J14)</f>
-      </c>
-      <c r="K15" s="7">
-        <f>SUM(K6:K14)</f>
-      </c>
-      <c r="L15" s="7">
-        <f>SUM(L6:L14)</f>
-      </c>
-      <c r="M15" s="7">
-        <f>SUM(M6:M14)</f>
-      </c>
-      <c r="N15" s="7">
-        <f>SUM(N6:N14)</f>
-      </c>
-      <c r="O15" s="7">
-        <f>SUM(O6:O14)</f>
-      </c>
-      <c r="P15" s="7">
-        <f>SUM(P6:P14)</f>
-      </c>
-      <c r="Q15" s="7">
-        <f>SUM(Q6:Q14)</f>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="7">
+        <f>SUM(B6:B15)</f>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C6:C15)</f>
+      </c>
+      <c r="D16" s="7">
+        <f>SUM(D6:D15)</f>
+      </c>
+      <c r="E16" s="7">
+        <f>SUM(E6:E15)</f>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(F6:F15)</f>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(G6:G15)</f>
+      </c>
+      <c r="H16" s="7">
+        <f>SUM(H6:H15)</f>
+      </c>
+      <c r="I16" s="7">
+        <f>SUM(I6:I15)</f>
+      </c>
+      <c r="J16" s="7">
+        <f>SUM(J6:J15)</f>
+      </c>
+      <c r="K16" s="7">
+        <f>SUM(K6:K15)</f>
+      </c>
+      <c r="L16" s="7">
+        <f>SUM(L6:L15)</f>
+      </c>
+      <c r="M16" s="7">
+        <f>SUM(M6:M15)</f>
+      </c>
+      <c r="N16" s="7">
+        <f>SUM(N6:N15)</f>
+      </c>
+      <c r="O16" s="7">
+        <f>SUM(O6:O15)</f>
+      </c>
+      <c r="P16" s="7">
+        <f>SUM(P6:P15)</f>
+      </c>
+      <c r="Q16" s="7">
+        <f>SUM(Q6:Q15)</f>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,7 +19,7 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Caliente vs Tecos</t>
+    <t>Juego Inaugural: Charros vs Tecos</t>
   </si>
   <si>
     <t>ZONA</t>
@@ -82,49 +82,46 @@
     <t>-</t>
   </si>
   <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>Butaca General</t>
+  </si>
+  <si>
+    <t>65.90%</t>
+  </si>
+  <si>
+    <t>Butaca Preferente</t>
+  </si>
+  <si>
+    <t>69.74%</t>
+  </si>
+  <si>
+    <t>Especial</t>
+  </si>
+  <si>
+    <t>Gradas</t>
+  </si>
+  <si>
+    <t>1.29%</t>
+  </si>
+  <si>
+    <t>Palcos</t>
+  </si>
+  <si>
     <t>100.00%</t>
   </si>
   <si>
-    <t>Butaca General</t>
-  </si>
-  <si>
-    <t>99.80%</t>
-  </si>
-  <si>
-    <t>Butaca Preferente</t>
-  </si>
-  <si>
-    <t>99.67%</t>
-  </si>
-  <si>
-    <t>Especial</t>
-  </si>
-  <si>
-    <t>26.00%</t>
-  </si>
-  <si>
-    <t>Gradas</t>
-  </si>
-  <si>
-    <t>39.75%</t>
-  </si>
-  <si>
-    <t>Palcos</t>
-  </si>
-  <si>
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>98.15%</t>
+    <t>40.74%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>SUITE</t>
-  </si>
-  <si>
-    <t>0.00%</t>
+    <t>56.48%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -133,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.39%</t>
+    <t>25.30%</t>
   </si>
 </sst>
 </file>
@@ -555,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -645,50 +642,50 @@
       <c r="B6" s="6">
         <v>100</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="6">
         <v>100</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="6">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,16 +696,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>1003</v>
+        <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>466</v>
+        <v>155</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6">
-        <v>55</v>
+      <c r="E7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -720,7 +717,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>474</v>
+        <v>176</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -735,16 +732,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1001</v>
+        <v>373</v>
       </c>
       <c r="Q7" s="6">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,16 +752,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="6">
-        <v>604</v>
+        <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -776,7 +773,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>385</v>
+        <v>531</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -790,17 +787,17 @@
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
+      <c r="N8" s="6">
+        <v>1</v>
+      </c>
+      <c r="O8" s="6">
+        <v>12</v>
       </c>
       <c r="P8" s="6">
-        <v>602</v>
+        <v>726</v>
       </c>
       <c r="Q8" s="6">
-        <v>2</v>
+        <v>315</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -819,8 +816,8 @@
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6">
-        <v>26</v>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -852,31 +849,31 @@
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="6">
-        <v>26</v>
+      <c r="P9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="Q9" s="6">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6">
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>828</v>
+        <v>32</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="6">
-        <v>285</v>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -905,22 +902,22 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+      <c r="O10" s="6">
+        <v>4</v>
       </c>
       <c r="P10" s="6">
-        <v>1113</v>
+        <v>36</v>
       </c>
       <c r="Q10" s="6">
-        <v>1687</v>
+        <v>2764</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6">
         <v>24</v>
@@ -931,8 +928,8 @@
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6">
-        <v>16</v>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -959,7 +956,7 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -971,7 +968,7 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -982,7 +979,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1000,7 +997,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1021,10 +1018,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="6">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1038,60 +1035,60 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
+        <v>9</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="6">
+        <v>48</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="6">
+        <v>4</v>
+      </c>
+      <c r="P13" s="6">
+        <v>61</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>47</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="6">
-        <v>72</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="6">
-        <v>108</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="6">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>22</v>
@@ -1136,126 +1133,70 @@
         <v>22</v>
       </c>
       <c r="Q14" s="6">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6">
-        <v>150</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>150</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="7">
+        <f>SUM(B6:B14)</f>
+      </c>
+      <c r="C15" s="7">
+        <f>SUM(C6:C14)</f>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D6:D14)</f>
+      </c>
+      <c r="E15" s="7">
+        <f>SUM(E6:E14)</f>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(F6:F14)</f>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(G6:G14)</f>
+      </c>
+      <c r="H15" s="7">
+        <f>SUM(H6:H14)</f>
+      </c>
+      <c r="I15" s="7">
+        <f>SUM(I6:I14)</f>
+      </c>
+      <c r="J15" s="7">
+        <f>SUM(J6:J14)</f>
+      </c>
+      <c r="K15" s="7">
+        <f>SUM(K6:K14)</f>
+      </c>
+      <c r="L15" s="7">
+        <f>SUM(L6:L14)</f>
+      </c>
+      <c r="M15" s="7">
+        <f>SUM(M6:M14)</f>
+      </c>
+      <c r="N15" s="7">
+        <f>SUM(N6:N14)</f>
+      </c>
+      <c r="O15" s="7">
+        <f>SUM(O6:O14)</f>
+      </c>
+      <c r="P15" s="7">
+        <f>SUM(P6:P14)</f>
+      </c>
+      <c r="Q15" s="7">
+        <f>SUM(Q6:Q14)</f>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(B6:B15)</f>
-      </c>
-      <c r="C16" s="7">
-        <f>SUM(C6:C15)</f>
-      </c>
-      <c r="D16" s="7">
-        <f>SUM(D6:D15)</f>
-      </c>
-      <c r="E16" s="7">
-        <f>SUM(E6:E15)</f>
-      </c>
-      <c r="F16" s="7">
-        <f>SUM(F6:F15)</f>
-      </c>
-      <c r="G16" s="7">
-        <f>SUM(G6:G15)</f>
-      </c>
-      <c r="H16" s="7">
-        <f>SUM(H6:H15)</f>
-      </c>
-      <c r="I16" s="7">
-        <f>SUM(I6:I15)</f>
-      </c>
-      <c r="J16" s="7">
-        <f>SUM(J6:J15)</f>
-      </c>
-      <c r="K16" s="7">
-        <f>SUM(K6:K15)</f>
-      </c>
-      <c r="L16" s="7">
-        <f>SUM(L6:L15)</f>
-      </c>
-      <c r="M16" s="7">
-        <f>SUM(M6:M15)</f>
-      </c>
-      <c r="N16" s="7">
-        <f>SUM(N6:N15)</f>
-      </c>
-      <c r="O16" s="7">
-        <f>SUM(O6:O15)</f>
-      </c>
-      <c r="P16" s="7">
-        <f>SUM(P6:P15)</f>
-      </c>
-      <c r="Q16" s="7">
-        <f>SUM(Q6:Q15)</f>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,13 +88,13 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>65.90%</t>
+    <t>66.78%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>69.74%</t>
+    <t>70.32%</t>
   </si>
   <si>
     <t>Especial</t>
@@ -103,7 +103,7 @@
     <t>Gradas</t>
   </si>
   <si>
-    <t>1.29%</t>
+    <t>1.68%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -121,7 +121,7 @@
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>56.48%</t>
+    <t>52.78%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -130,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>25.30%</t>
+    <t>25.66%</t>
   </si>
 </sst>
 </file>
@@ -699,7 +699,7 @@
         <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -738,10 +738,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="Q7" s="6">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,7 +755,7 @@
         <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -791,13 +791,13 @@
         <v>1</v>
       </c>
       <c r="O8" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P8" s="6">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="Q8" s="6">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -867,7 +867,7 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -902,14 +902,14 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6">
-        <v>4</v>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="Q10" s="6">
-        <v>2764</v>
+        <v>2753</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -1070,14 +1070,14 @@
       <c r="N13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="6">
-        <v>4</v>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="Q13" s="6">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>36</v>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,13 +88,13 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>66.78%</t>
+    <t>67.49%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>70.32%</t>
+    <t>71.57%</t>
   </si>
   <si>
     <t>Especial</t>
@@ -121,7 +121,7 @@
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>52.78%</t>
+    <t>58.33%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -130,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>25.66%</t>
+    <t>26.12%</t>
   </si>
 </sst>
 </file>
@@ -699,7 +699,7 @@
         <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -738,10 +738,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="Q7" s="6">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,7 +755,7 @@
         <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -794,10 +794,10 @@
         <v>10</v>
       </c>
       <c r="P8" s="6">
-        <v>732</v>
+        <v>745</v>
       </c>
       <c r="Q8" s="6">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1070,14 +1070,14 @@
       <c r="N13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
+      <c r="O13" s="6">
+        <v>4</v>
       </c>
       <c r="P13" s="6">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="6">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>36</v>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -88,13 +88,13 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>67.49%</t>
+    <t>69.61%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>71.57%</t>
+    <t>75.22%</t>
   </si>
   <si>
     <t>Especial</t>
@@ -103,7 +103,7 @@
     <t>Gradas</t>
   </si>
   <si>
-    <t>1.68%</t>
+    <t>5.79%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -115,13 +115,13 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>40.74%</t>
+    <t>48.15%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>58.33%</t>
+    <t>56.48%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -130,7 +130,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>26.12%</t>
+    <t>29.54%</t>
   </si>
 </sst>
 </file>
@@ -699,7 +699,7 @@
         <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -738,10 +738,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="Q7" s="6">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,7 +755,7 @@
         <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -791,13 +791,13 @@
         <v>1</v>
       </c>
       <c r="O8" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P8" s="6">
-        <v>745</v>
+        <v>783</v>
       </c>
       <c r="Q8" s="6">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -867,13 +867,13 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
+      <c r="E10" s="6">
+        <v>104</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -906,10 +906,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="Q10" s="6">
-        <v>2753</v>
+        <v>2638</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -979,7 +979,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1018,10 +1018,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="Q12" s="6">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1035,7 +1035,7 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1070,14 +1070,14 @@
       <c r="N13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="6">
-        <v>4</v>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="6">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>36</v>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,22 +88,25 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>69.61%</t>
+    <t>74.20%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>75.22%</t>
+    <t>78.10%</t>
   </si>
   <si>
     <t>Especial</t>
   </si>
   <si>
+    <t>4.00%</t>
+  </si>
+  <si>
     <t>Gradas</t>
   </si>
   <si>
-    <t>5.79%</t>
+    <t>6.50%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -115,13 +118,13 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>48.15%</t>
+    <t>50.00%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>56.48%</t>
+    <t>58.33%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -130,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>29.54%</t>
+    <t>31.22%</t>
   </si>
 </sst>
 </file>
@@ -699,7 +702,7 @@
         <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -717,7 +720,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -732,16 +735,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>42</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+        <v>40</v>
+      </c>
+      <c r="O7" s="6">
+        <v>10</v>
       </c>
       <c r="P7" s="6">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="Q7" s="6">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,13 +758,13 @@
         <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -787,17 +790,17 @@
       <c r="M8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="6">
-        <v>1</v>
+      <c r="N8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O8" s="6">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="P8" s="6">
-        <v>783</v>
+        <v>813</v>
       </c>
       <c r="Q8" s="6">
-        <v>258</v>
+        <v>228</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -828,8 +831,8 @@
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
+      <c r="I9" s="6">
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -849,31 +852,31 @@
       <c r="O9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="6" t="s">
-        <v>22</v>
+      <c r="P9" s="6">
+        <v>4</v>
       </c>
       <c r="Q9" s="6">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6">
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -906,18 +909,18 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="Q10" s="6">
-        <v>2638</v>
+        <v>2618</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="6">
         <v>24</v>
@@ -940,8 +943,8 @@
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
+      <c r="I11" s="6">
+        <v>12</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -956,7 +959,7 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -968,18 +971,18 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="6">
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1018,24 +1021,24 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q12" s="6">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="6">
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1074,18 +1077,18 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="6">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="6">
         <v>150</v>
@@ -1141,7 +1144,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="7">
         <f>SUM(B6:B14)</f>
@@ -1192,7 +1195,7 @@
         <f>SUM(Q6:Q14)</f>
       </c>
       <c r="R15" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,25 +88,25 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>74.20%</t>
+    <t>79.33%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>78.10%</t>
+    <t>85.59%</t>
   </si>
   <si>
     <t>Especial</t>
   </si>
   <si>
-    <t>4.00%</t>
+    <t>27.00%</t>
   </si>
   <si>
     <t>Gradas</t>
   </si>
   <si>
-    <t>6.50%</t>
+    <t>7.89%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -118,13 +118,13 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>50.00%</t>
+    <t>65.74%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>58.33%</t>
+    <t>71.30%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>31.22%</t>
+    <t>35.22%</t>
   </si>
 </sst>
 </file>
@@ -702,7 +702,7 @@
         <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -737,14 +737,14 @@
       <c r="N7" s="6">
         <v>40</v>
       </c>
-      <c r="O7" s="6">
-        <v>10</v>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="Q7" s="6">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>252</v>
+        <v>350</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -793,14 +793,14 @@
       <c r="N8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="6">
-        <v>20</v>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>813</v>
+        <v>891</v>
       </c>
       <c r="Q8" s="6">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -819,8 +819,8 @@
       <c r="D9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>22</v>
+      <c r="E9" s="6">
+        <v>23</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -853,10 +853,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="Q9" s="6">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -870,7 +870,7 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -909,10 +909,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="Q10" s="6">
-        <v>2618</v>
+        <v>2579</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -982,7 +982,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1021,10 +1021,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="Q12" s="6">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1038,7 +1038,7 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1077,10 +1077,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="Q13" s="6">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,13 +88,13 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>79.33%</t>
+    <t>86.93%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>85.59%</t>
+    <t>89.05%</t>
   </si>
   <si>
     <t>Especial</t>
@@ -106,7 +106,7 @@
     <t>Gradas</t>
   </si>
   <si>
-    <t>7.89%</t>
+    <t>10.71%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -118,13 +118,13 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>65.74%</t>
+    <t>67.59%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>71.30%</t>
+    <t>76.85%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>35.22%</t>
+    <t>38.54%</t>
   </si>
 </sst>
 </file>
@@ -702,13 +702,13 @@
         <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -737,14 +737,14 @@
       <c r="N7" s="6">
         <v>40</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="O7" s="6">
+        <v>11</v>
       </c>
       <c r="P7" s="6">
-        <v>449</v>
+        <v>492</v>
       </c>
       <c r="Q7" s="6">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -758,13 +758,13 @@
         <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -793,14 +793,14 @@
       <c r="N8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="6" t="s">
-        <v>22</v>
+      <c r="O8" s="6">
+        <v>2</v>
       </c>
       <c r="P8" s="6">
-        <v>891</v>
+        <v>927</v>
       </c>
       <c r="Q8" s="6">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -870,13 +870,13 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -905,14 +905,14 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+      <c r="O10" s="6">
+        <v>2</v>
       </c>
       <c r="P10" s="6">
-        <v>221</v>
+        <v>300</v>
       </c>
       <c r="Q10" s="6">
-        <v>2579</v>
+        <v>2500</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -982,7 +982,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1021,10 +1021,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q12" s="6">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1038,7 +1038,7 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1077,10 +1077,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="Q13" s="6">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -88,25 +88,25 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>86.93%</t>
+    <t>91.70%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>89.05%</t>
+    <t>92.12%</t>
   </si>
   <si>
     <t>Especial</t>
   </si>
   <si>
-    <t>27.00%</t>
+    <t>31.00%</t>
   </si>
   <si>
     <t>Gradas</t>
   </si>
   <si>
-    <t>10.71%</t>
+    <t>11.93%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -118,13 +118,13 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>67.59%</t>
+    <t>73.15%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>76.85%</t>
+    <t>85.19%</t>
   </si>
   <si>
     <t>Tecobar</t>
@@ -133,7 +133,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>38.54%</t>
+    <t>40.78%</t>
   </si>
 </sst>
 </file>
@@ -702,7 +702,7 @@
         <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -735,16 +735,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O7" s="6">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P7" s="6">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="Q7" s="6">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -758,7 +758,7 @@
         <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -793,14 +793,14 @@
       <c r="N8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="6">
-        <v>2</v>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>927</v>
+        <v>959</v>
       </c>
       <c r="Q8" s="6">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -820,7 +820,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -853,10 +853,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="6">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -870,13 +870,13 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -905,14 +905,14 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6">
-        <v>2</v>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="Q10" s="6">
-        <v>2500</v>
+        <v>2466</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -982,7 +982,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1021,10 +1021,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="6">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>35</v>
@@ -1038,7 +1038,7 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1077,10 +1077,10 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="Q13" s="6">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>37</v>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,7 +19,7 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Charros vs Tecos</t>
+    <t>Juego Inaugural: Caliente vs Tecos</t>
   </si>
   <si>
     <t>ZONA</t>
@@ -82,58 +82,58 @@
     <t>-</t>
   </si>
   <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>Butaca General</t>
+  </si>
+  <si>
+    <t>99.80%</t>
+  </si>
+  <si>
+    <t>Butaca Preferente</t>
+  </si>
+  <si>
+    <t>99.67%</t>
+  </si>
+  <si>
+    <t>Especial</t>
+  </si>
+  <si>
+    <t>26.00%</t>
+  </si>
+  <si>
+    <t>Gradas</t>
+  </si>
+  <si>
+    <t>39.75%</t>
+  </si>
+  <si>
+    <t>Palcos</t>
+  </si>
+  <si>
+    <t>Palcos 1ra</t>
+  </si>
+  <si>
+    <t>98.15%</t>
+  </si>
+  <si>
+    <t>Palcos 3ra</t>
+  </si>
+  <si>
+    <t>SUITE</t>
+  </si>
+  <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>Butaca General</t>
-  </si>
-  <si>
-    <t>91.70%</t>
-  </si>
-  <si>
-    <t>Butaca Preferente</t>
-  </si>
-  <si>
-    <t>92.12%</t>
-  </si>
-  <si>
-    <t>Especial</t>
-  </si>
-  <si>
-    <t>31.00%</t>
-  </si>
-  <si>
-    <t>Gradas</t>
-  </si>
-  <si>
-    <t>11.93%</t>
-  </si>
-  <si>
-    <t>Palcos</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>Palcos 1ra</t>
-  </si>
-  <si>
-    <t>73.15%</t>
-  </si>
-  <si>
-    <t>Palcos 3ra</t>
-  </si>
-  <si>
-    <t>85.19%</t>
-  </si>
-  <si>
     <t>Tecobar</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>40.78%</t>
+    <t>61.39%</t>
   </si>
 </sst>
 </file>
@@ -555,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -645,8 +645,8 @@
       <c r="B6" s="6">
         <v>100</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
+      <c r="C6" s="6">
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -684,11 +684,11 @@
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" s="6">
+      <c r="P6" s="6">
         <v>100</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -699,16 +699,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>566</v>
+        <v>1003</v>
       </c>
       <c r="C7" s="6">
-        <v>258</v>
+        <v>466</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -720,7 +720,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>183</v>
+        <v>474</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -735,16 +735,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>48</v>
-      </c>
-      <c r="O7" s="6">
-        <v>20</v>
+        <v>6</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>519</v>
+        <v>1001</v>
       </c>
       <c r="Q7" s="6">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,16 +755,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="6">
-        <v>1041</v>
+        <v>604</v>
       </c>
       <c r="C8" s="6">
-        <v>416</v>
+        <v>217</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6">
-        <v>12</v>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -776,7 +776,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>531</v>
+        <v>385</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -797,10 +797,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>959</v>
+        <v>602</v>
       </c>
       <c r="Q8" s="6">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -820,7 +820,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -831,8 +831,8 @@
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6">
-        <v>4</v>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -853,10 +853,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q9" s="6">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -870,13 +870,13 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>175</v>
+        <v>828</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>159</v>
+        <v>285</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -909,10 +909,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>334</v>
+        <v>1113</v>
       </c>
       <c r="Q10" s="6">
-        <v>2466</v>
+        <v>1687</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -931,8 +931,8 @@
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+      <c r="E11" s="6">
+        <v>16</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -943,8 +943,8 @@
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6">
-        <v>12</v>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -959,7 +959,7 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -971,18 +971,18 @@
         <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1000,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1021,24 +1021,24 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="Q12" s="6">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6">
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1056,7 +1056,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="6">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1077,129 +1077,185 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>92</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>16</v>
+        <v>108</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="6">
+        <v>20</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>20</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B15" s="6">
         <v>150</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q14" s="6">
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="6">
         <v>150</v>
       </c>
-      <c r="R14" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="R15" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(B6:B14)</f>
-      </c>
-      <c r="C15" s="7">
-        <f>SUM(C6:C14)</f>
-      </c>
-      <c r="D15" s="7">
-        <f>SUM(D6:D14)</f>
-      </c>
-      <c r="E15" s="7">
-        <f>SUM(E6:E14)</f>
-      </c>
-      <c r="F15" s="7">
-        <f>SUM(F6:F14)</f>
-      </c>
-      <c r="G15" s="7">
-        <f>SUM(G6:G14)</f>
-      </c>
-      <c r="H15" s="7">
-        <f>SUM(H6:H14)</f>
-      </c>
-      <c r="I15" s="7">
-        <f>SUM(I6:I14)</f>
-      </c>
-      <c r="J15" s="7">
-        <f>SUM(J6:J14)</f>
-      </c>
-      <c r="K15" s="7">
-        <f>SUM(K6:K14)</f>
-      </c>
-      <c r="L15" s="7">
-        <f>SUM(L6:L14)</f>
-      </c>
-      <c r="M15" s="7">
-        <f>SUM(M6:M14)</f>
-      </c>
-      <c r="N15" s="7">
-        <f>SUM(N6:N14)</f>
-      </c>
-      <c r="O15" s="7">
-        <f>SUM(O6:O14)</f>
-      </c>
-      <c r="P15" s="7">
-        <f>SUM(P6:P14)</f>
-      </c>
-      <c r="Q15" s="7">
-        <f>SUM(Q6:Q14)</f>
-      </c>
-      <c r="R15" s="7" t="s">
+      <c r="B16" s="7">
+        <f>SUM(B6:B15)</f>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C6:C15)</f>
+      </c>
+      <c r="D16" s="7">
+        <f>SUM(D6:D15)</f>
+      </c>
+      <c r="E16" s="7">
+        <f>SUM(E6:E15)</f>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(F6:F15)</f>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(G6:G15)</f>
+      </c>
+      <c r="H16" s="7">
+        <f>SUM(H6:H15)</f>
+      </c>
+      <c r="I16" s="7">
+        <f>SUM(I6:I15)</f>
+      </c>
+      <c r="J16" s="7">
+        <f>SUM(J6:J15)</f>
+      </c>
+      <c r="K16" s="7">
+        <f>SUM(K6:K15)</f>
+      </c>
+      <c r="L16" s="7">
+        <f>SUM(L6:L15)</f>
+      </c>
+      <c r="M16" s="7">
+        <f>SUM(M6:M15)</f>
+      </c>
+      <c r="N16" s="7">
+        <f>SUM(N6:N15)</f>
+      </c>
+      <c r="O16" s="7">
+        <f>SUM(O6:O15)</f>
+      </c>
+      <c r="P16" s="7">
+        <f>SUM(P6:P15)</f>
+      </c>
+      <c r="Q16" s="7">
+        <f>SUM(Q6:Q15)</f>
+      </c>
+      <c r="R16" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="40">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,7 +19,7 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Caliente vs Tecos</t>
+    <t>Juego Inaugural: Charros vs Tecos</t>
   </si>
   <si>
     <t>ZONA</t>
@@ -88,25 +88,25 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>99.80%</t>
+    <t>99.47%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>99.67%</t>
+    <t>97.69%</t>
   </si>
   <si>
     <t>Especial</t>
   </si>
   <si>
-    <t>26.00%</t>
+    <t>72.00%</t>
   </si>
   <si>
     <t>Gradas</t>
   </si>
   <si>
-    <t>39.75%</t>
+    <t>25.29%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -115,25 +115,22 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>98.15%</t>
+    <t>99.07%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
-    <t>SUITE</t>
+    <t>Tecobar</t>
   </si>
   <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>Tecobar</t>
-  </si>
-  <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.39%</t>
+    <t>53.99%</t>
   </si>
 </sst>
 </file>
@@ -555,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -699,16 +696,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>1003</v>
+        <v>566</v>
       </c>
       <c r="C7" s="6">
-        <v>466</v>
+        <v>322</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -720,7 +717,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>474</v>
+        <v>183</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -734,17 +731,17 @@
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="6">
-        <v>6</v>
+      <c r="N7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1001</v>
+        <v>563</v>
       </c>
       <c r="Q7" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -755,16 +752,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="6">
-        <v>604</v>
+        <v>1041</v>
       </c>
       <c r="C8" s="6">
-        <v>217</v>
+        <v>489</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>22</v>
+      <c r="E8" s="6">
+        <v>14</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -776,7 +773,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>385</v>
+        <v>514</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -797,10 +794,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>602</v>
+        <v>1017</v>
       </c>
       <c r="Q8" s="6">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -820,7 +817,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -831,8 +828,8 @@
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>22</v>
+      <c r="I9" s="6">
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -853,10 +850,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="6">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -870,13 +867,13 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>828</v>
+        <v>466</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -909,10 +906,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>1113</v>
+        <v>708</v>
       </c>
       <c r="Q10" s="6">
-        <v>1687</v>
+        <v>2092</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -931,8 +928,8 @@
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6">
-        <v>16</v>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -943,8 +940,8 @@
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>22</v>
+      <c r="I11" s="6">
+        <v>12</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -959,7 +956,7 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -982,7 +979,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1000,7 +997,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1021,10 +1018,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q12" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1038,7 +1035,7 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1056,7 +1053,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="6">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1077,13 +1074,13 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>108</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>22</v>
+        <v>107</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>1</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1091,7 +1088,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="6">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>22</v>
@@ -1136,126 +1133,70 @@
         <v>22</v>
       </c>
       <c r="Q14" s="6">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6">
-        <v>150</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>150</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="7">
+        <f>SUM(B6:B14)</f>
+      </c>
+      <c r="C15" s="7">
+        <f>SUM(C6:C14)</f>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D6:D14)</f>
+      </c>
+      <c r="E15" s="7">
+        <f>SUM(E6:E14)</f>
+      </c>
+      <c r="F15" s="7">
+        <f>SUM(F6:F14)</f>
+      </c>
+      <c r="G15" s="7">
+        <f>SUM(G6:G14)</f>
+      </c>
+      <c r="H15" s="7">
+        <f>SUM(H6:H14)</f>
+      </c>
+      <c r="I15" s="7">
+        <f>SUM(I6:I14)</f>
+      </c>
+      <c r="J15" s="7">
+        <f>SUM(J6:J14)</f>
+      </c>
+      <c r="K15" s="7">
+        <f>SUM(K6:K14)</f>
+      </c>
+      <c r="L15" s="7">
+        <f>SUM(L6:L14)</f>
+      </c>
+      <c r="M15" s="7">
+        <f>SUM(M6:M14)</f>
+      </c>
+      <c r="N15" s="7">
+        <f>SUM(N6:N14)</f>
+      </c>
+      <c r="O15" s="7">
+        <f>SUM(O6:O14)</f>
+      </c>
+      <c r="P15" s="7">
+        <f>SUM(P6:P14)</f>
+      </c>
+      <c r="Q15" s="7">
+        <f>SUM(Q6:Q14)</f>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(B6:B15)</f>
-      </c>
-      <c r="C16" s="7">
-        <f>SUM(C6:C15)</f>
-      </c>
-      <c r="D16" s="7">
-        <f>SUM(D6:D15)</f>
-      </c>
-      <c r="E16" s="7">
-        <f>SUM(E6:E15)</f>
-      </c>
-      <c r="F16" s="7">
-        <f>SUM(F6:F15)</f>
-      </c>
-      <c r="G16" s="7">
-        <f>SUM(G6:G15)</f>
-      </c>
-      <c r="H16" s="7">
-        <f>SUM(H6:H15)</f>
-      </c>
-      <c r="I16" s="7">
-        <f>SUM(I6:I15)</f>
-      </c>
-      <c r="J16" s="7">
-        <f>SUM(J6:J15)</f>
-      </c>
-      <c r="K16" s="7">
-        <f>SUM(K6:K15)</f>
-      </c>
-      <c r="L16" s="7">
-        <f>SUM(L6:L15)</f>
-      </c>
-      <c r="M16" s="7">
-        <f>SUM(M6:M15)</f>
-      </c>
-      <c r="N16" s="7">
-        <f>SUM(N6:N15)</f>
-      </c>
-      <c r="O16" s="7">
-        <f>SUM(O6:O15)</f>
-      </c>
-      <c r="P16" s="7">
-        <f>SUM(P6:P15)</f>
-      </c>
-      <c r="Q16" s="7">
-        <f>SUM(Q6:Q15)</f>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Tecos 2026.xlsx
+++ b/data/asistencia/Tecos 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,7 +19,7 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Charros vs Tecos</t>
+    <t>Juego Inaugural: Caliente vs Tecos</t>
   </si>
   <si>
     <t>ZONA</t>
@@ -88,25 +88,25 @@
     <t>Butaca General</t>
   </si>
   <si>
-    <t>99.47%</t>
+    <t>99.80%</t>
   </si>
   <si>
     <t>Butaca Preferente</t>
   </si>
   <si>
-    <t>97.69%</t>
+    <t>99.67%</t>
   </si>
   <si>
     <t>Especial</t>
   </si>
   <si>
-    <t>72.00%</t>
+    <t>26.00%</t>
   </si>
   <si>
     <t>Gradas</t>
   </si>
   <si>
-    <t>25.29%</t>
+    <t>39.75%</t>
   </si>
   <si>
     <t>Palcos</t>
@@ -115,22 +115,25 @@
     <t>Palcos 1ra</t>
   </si>
   <si>
-    <t>99.07%</t>
+    <t>98.15%</t>
   </si>
   <si>
     <t>Palcos 3ra</t>
   </si>
   <si>
+    <t>SUITE</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
     <t>Tecobar</t>
   </si>
   <si>
-    <t>0.00%</t>
-  </si>
-  <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>53.99%</t>
+    <t>61.39%</t>
   </si>
 </sst>
 </file>
@@ -552,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -696,16 +699,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>566</v>
+        <v>1003</v>
       </c>
       <c r="C7" s="6">
-        <v>322</v>
+        <v>466</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -717,7 +720,7 @@
         <v>22</v>
       </c>
       <c r="I7" s="6">
-        <v>183</v>
+        <v>474</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>22</v>
@@ -731,17 +734,17 @@
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>22</v>
+      <c r="N7" s="6">
+        <v>6</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>563</v>
+        <v>1001</v>
       </c>
       <c r="Q7" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -752,16 +755,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="6">
-        <v>1041</v>
+        <v>604</v>
       </c>
       <c r="C8" s="6">
-        <v>489</v>
+        <v>217</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6">
-        <v>14</v>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>22</v>
@@ -773,7 +776,7 @@
         <v>22</v>
       </c>
       <c r="I8" s="6">
-        <v>514</v>
+        <v>385</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>22</v>
@@ -794,10 +797,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>1017</v>
+        <v>602</v>
       </c>
       <c r="Q8" s="6">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>27</v>
@@ -817,7 +820,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="6">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>22</v>
@@ -828,8 +831,8 @@
       <c r="H9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="6">
-        <v>4</v>
+      <c r="I9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -850,10 +853,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="Q9" s="6">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -867,13 +870,13 @@
         <v>2800</v>
       </c>
       <c r="C10" s="6">
-        <v>466</v>
+        <v>828</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -906,10 +909,10 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>708</v>
+        <v>1113</v>
       </c>
       <c r="Q10" s="6">
-        <v>2092</v>
+        <v>1687</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>31</v>
@@ -928,8 +931,8 @@
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
+      <c r="E11" s="6">
+        <v>16</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -940,8 +943,8 @@
       <c r="H11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="6">
-        <v>12</v>
+      <c r="I11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -956,7 +959,7 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -979,7 +982,7 @@
         <v>108</v>
       </c>
       <c r="C12" s="6">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -997,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="6">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>22</v>
@@ -1018,10 +1021,10 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q12" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1035,7 +1038,7 @@
         <v>108</v>
       </c>
       <c r="C13" s="6">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>22</v>
@@ -1053,7 +1056,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="6">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1074,13 +1077,13 @@
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>107</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>1</v>
+        <v>108</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1088,7 +1091,7 @@
         <v>36</v>
       </c>
       <c r="B14" s="6">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>22</v>
@@ -1133,70 +1136,126 @@
         <v>22</v>
       </c>
       <c r="Q14" s="6">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(B6:B14)</f>
-      </c>
-      <c r="C15" s="7">
-        <f>SUM(C6:C14)</f>
-      </c>
-      <c r="D15" s="7">
-        <f>SUM(D6:D14)</f>
-      </c>
-      <c r="E15" s="7">
-        <f>SUM(E6:E14)</f>
-      </c>
-      <c r="F15" s="7">
-        <f>SUM(F6:F14)</f>
-      </c>
-      <c r="G15" s="7">
-        <f>SUM(G6:G14)</f>
-      </c>
-      <c r="H15" s="7">
-        <f>SUM(H6:H14)</f>
-      </c>
-      <c r="I15" s="7">
-        <f>SUM(I6:I14)</f>
-      </c>
-      <c r="J15" s="7">
-        <f>SUM(J6:J14)</f>
-      </c>
-      <c r="K15" s="7">
-        <f>SUM(K6:K14)</f>
-      </c>
-      <c r="L15" s="7">
-        <f>SUM(L6:L14)</f>
-      </c>
-      <c r="M15" s="7">
-        <f>SUM(M6:M14)</f>
-      </c>
-      <c r="N15" s="7">
-        <f>SUM(N6:N14)</f>
-      </c>
-      <c r="O15" s="7">
-        <f>SUM(O6:O14)</f>
-      </c>
-      <c r="P15" s="7">
-        <f>SUM(P6:P14)</f>
-      </c>
-      <c r="Q15" s="7">
-        <f>SUM(Q6:Q14)</f>
-      </c>
-      <c r="R15" s="7" t="s">
+      <c r="B15" s="6">
+        <v>150</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>150</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="7">
+        <f>SUM(B6:B15)</f>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C6:C15)</f>
+      </c>
+      <c r="D16" s="7">
+        <f>SUM(D6:D15)</f>
+      </c>
+      <c r="E16" s="7">
+        <f>SUM(E6:E15)</f>
+      </c>
+      <c r="F16" s="7">
+        <f>SUM(F6:F15)</f>
+      </c>
+      <c r="G16" s="7">
+        <f>SUM(G6:G15)</f>
+      </c>
+      <c r="H16" s="7">
+        <f>SUM(H6:H15)</f>
+      </c>
+      <c r="I16" s="7">
+        <f>SUM(I6:I15)</f>
+      </c>
+      <c r="J16" s="7">
+        <f>SUM(J6:J15)</f>
+      </c>
+      <c r="K16" s="7">
+        <f>SUM(K6:K15)</f>
+      </c>
+      <c r="L16" s="7">
+        <f>SUM(L6:L15)</f>
+      </c>
+      <c r="M16" s="7">
+        <f>SUM(M6:M15)</f>
+      </c>
+      <c r="N16" s="7">
+        <f>SUM(N6:N15)</f>
+      </c>
+      <c r="O16" s="7">
+        <f>SUM(O6:O15)</f>
+      </c>
+      <c r="P16" s="7">
+        <f>SUM(P6:P15)</f>
+      </c>
+      <c r="Q16" s="7">
+        <f>SUM(Q6:Q15)</f>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
     </row>
